--- a/artfynd/A 13834-2025 artfynd.xlsx
+++ b/artfynd/A 13834-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,53 +792,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2676927</v>
+        <v>4173984</v>
       </c>
       <c r="B3" t="n">
-        <v>106707</v>
+        <v>95511</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220204</v>
+        <v>221944</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Glänta nära utfarten mot landsvägen, Vstm</t>
+          <t>Häll i granskogen ca 300 m N om vägen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546572.091310487</v>
+        <v>546537.5704414711</v>
       </c>
       <c r="R3" t="n">
-        <v>6657204.521206533</v>
+        <v>6657481.311729174</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,11 +889,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Gödningspåverkad gräsmark</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -906,6 +901,123 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2676927</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106707</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Glänta nära utfarten mot landsvägen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>546572.091310487</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6657204.521206533</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2012-05-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2012-05-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gödningspåverkad gräsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Jacobson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Jacobson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
